--- a/data/test_data.xlsx
+++ b/data/test_data.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11008"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10311"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michaelhunt/github/r-workshop/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michaelhunt/Documents/Rcode/r-workshop/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0EC51A99-6E6F-9B4D-994D-5286756C7532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BD93DBA-56F8-A041-878F-AC3E913A4C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4700" yWindow="5320" windowWidth="24440" windowHeight="12940" xr2:uid="{A94005A5-42DF-7E46-821E-3AF3F001110E}"/>
+    <workbookView xWindow="1900" yWindow="1820" windowWidth="27240" windowHeight="16440" xr2:uid="{4E2A78B5-8169-6445-800A-508326C8897D}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="regression" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -48,24 +48,35 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -73,12 +84,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="22"/>
+      </left>
+      <right style="thin">
+        <color indexed="22"/>
+      </right>
+      <top style="thin">
+        <color indexed="22"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="22"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0" hidden="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -107,39 +136,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -191,7 +220,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -302,13 +331,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -317,6 +339,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -381,19 +410,39 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7104C785-5C9C-2B40-81F9-614D5A8C395A}">
-  <dimension ref="A1:B6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8974B210-470B-6C4E-B744-DD651D8FE1E5}">
+  <dimension ref="A1:B100"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
@@ -405,43 +454,795 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
+      <c r="A2" s="1">
+        <v>51</v>
+      </c>
+      <c r="B2" s="1">
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
+      <c r="A3" s="1">
+        <v>53</v>
+      </c>
+      <c r="B3" s="1">
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
+      <c r="A4" s="1">
+        <v>67</v>
+      </c>
+      <c r="B4" s="1">
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
+      <c r="A5" s="1">
+        <v>64</v>
+      </c>
+      <c r="B5" s="1">
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
+      <c r="A6" s="1">
+        <v>61</v>
+      </c>
+      <c r="B6" s="1">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>59</v>
+      </c>
+      <c r="B7" s="1">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>69</v>
+      </c>
+      <c r="B8" s="1">
+        <v>66.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>67</v>
+      </c>
+      <c r="B9" s="1">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>54</v>
+      </c>
+      <c r="B10" s="1">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>60</v>
+      </c>
+      <c r="B11" s="1">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>45</v>
+      </c>
+      <c r="B12" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>55</v>
+      </c>
+      <c r="B13" s="1">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>58</v>
+      </c>
+      <c r="B14" s="1">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>64</v>
+      </c>
+      <c r="B15" s="1">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>54</v>
+      </c>
+      <c r="B16" s="1">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>64</v>
+      </c>
+      <c r="B17" s="1">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>62</v>
+      </c>
+      <c r="B18" s="1">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>69</v>
+      </c>
+      <c r="B19" s="1">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>45</v>
+      </c>
+      <c r="B20" s="1">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>71</v>
+      </c>
+      <c r="B21" s="1">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>57</v>
+      </c>
+      <c r="B22" s="1">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>51</v>
+      </c>
+      <c r="B23" s="1">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>45</v>
+      </c>
+      <c r="B24" s="1">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>60</v>
+      </c>
+      <c r="B25" s="1">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
+        <v>51</v>
+      </c>
+      <c r="B26" s="1">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
+        <v>62</v>
+      </c>
+      <c r="B27" s="1">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
+        <v>59</v>
+      </c>
+      <c r="B28" s="1">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
+        <v>63</v>
+      </c>
+      <c r="B29" s="1">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" s="1">
+        <v>56</v>
+      </c>
+      <c r="B30" s="1">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31" s="1">
+        <v>54</v>
+      </c>
+      <c r="B31" s="1">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
+        <v>63</v>
+      </c>
+      <c r="B32" s="1">
+        <v>70.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
+        <v>64</v>
+      </c>
+      <c r="B33" s="1">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" s="1">
+        <v>58</v>
+      </c>
+      <c r="B34" s="1">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
+        <v>60</v>
+      </c>
+      <c r="B35" s="1">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
+        <v>62</v>
+      </c>
+      <c r="B36" s="1">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" s="1">
+        <v>70</v>
+      </c>
+      <c r="B37" s="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" s="1">
+        <v>61</v>
+      </c>
+      <c r="B38" s="1">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" s="1">
+        <v>60</v>
+      </c>
+      <c r="B39" s="1">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" s="1">
+        <v>58</v>
+      </c>
+      <c r="B40" s="1">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" s="1">
+        <v>60</v>
+      </c>
+      <c r="B41" s="1">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" s="1">
+        <v>48</v>
+      </c>
+      <c r="B42" s="1">
+        <v>47.5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" s="1">
+        <v>49</v>
+      </c>
+      <c r="B43" s="1">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44" s="1">
+        <v>57</v>
+      </c>
+      <c r="B44" s="1">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" s="1">
+        <v>62</v>
+      </c>
+      <c r="B45" s="1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" s="1">
+        <v>68</v>
+      </c>
+      <c r="B46" s="1">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47" s="1">
+        <v>64</v>
+      </c>
+      <c r="B47" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48" s="1">
+        <v>51</v>
+      </c>
+      <c r="B48" s="1">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49" s="1">
+        <v>59</v>
+      </c>
+      <c r="B49" s="1">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50" s="1">
+        <v>51</v>
+      </c>
+      <c r="B50" s="1">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A51" s="1">
+        <v>58</v>
+      </c>
+      <c r="B51" s="1">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52" s="1">
+        <v>60</v>
+      </c>
+      <c r="B52" s="1">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53" s="1">
+        <v>66</v>
+      </c>
+      <c r="B53" s="1">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54" s="1">
+        <v>52</v>
+      </c>
+      <c r="B54" s="1">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55" s="1">
+        <v>61</v>
+      </c>
+      <c r="B55" s="1">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A56" s="1">
+        <v>51</v>
+      </c>
+      <c r="B56" s="1">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A57" s="1">
+        <v>53</v>
+      </c>
+      <c r="B57" s="1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A58" s="1">
+        <v>50</v>
+      </c>
+      <c r="B58" s="1">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A59" s="1">
+        <v>68</v>
+      </c>
+      <c r="B59" s="1">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A60" s="1">
+        <v>64</v>
+      </c>
+      <c r="B60" s="1">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A61" s="1">
+        <v>63</v>
+      </c>
+      <c r="B61" s="1">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A62" s="1">
+        <v>54</v>
+      </c>
+      <c r="B62" s="1">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A63" s="1">
+        <v>59</v>
+      </c>
+      <c r="B63" s="1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A64" s="1">
+        <v>50</v>
+      </c>
+      <c r="B64" s="1">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A65" s="1">
+        <v>53</v>
+      </c>
+      <c r="B65" s="1">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A66" s="1">
+        <v>61</v>
+      </c>
+      <c r="B66" s="1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A67" s="1">
+        <v>58</v>
+      </c>
+      <c r="B67" s="1">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A68" s="1">
+        <v>63</v>
+      </c>
+      <c r="B68" s="1">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A69" s="1">
+        <v>44</v>
+      </c>
+      <c r="B69" s="1">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A70" s="1">
+        <v>53</v>
+      </c>
+      <c r="B70" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A71" s="1">
+        <v>64</v>
+      </c>
+      <c r="B71" s="1">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A72" s="1">
+        <v>55</v>
+      </c>
+      <c r="B72" s="1">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A73" s="1">
+        <v>55</v>
+      </c>
+      <c r="B73" s="1">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A74" s="1">
+        <v>66</v>
+      </c>
+      <c r="B74" s="1">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A75" s="1">
+        <v>69</v>
+      </c>
+      <c r="B75" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A76" s="1">
+        <v>53</v>
+      </c>
+      <c r="B76" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A77" s="1">
+        <v>51</v>
+      </c>
+      <c r="B77" s="1">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A78" s="1">
+        <v>62</v>
+      </c>
+      <c r="B78" s="1">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A79" s="1">
+        <v>61</v>
+      </c>
+      <c r="B79" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A80" s="1">
+        <v>56</v>
+      </c>
+      <c r="B80" s="1">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A81" s="1">
+        <v>59</v>
+      </c>
+      <c r="B81" s="1">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A82" s="1">
+        <v>67</v>
+      </c>
+      <c r="B82" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A83" s="1">
+        <v>54</v>
+      </c>
+      <c r="B83" s="1">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A84" s="1">
+        <v>55</v>
+      </c>
+      <c r="B84" s="1">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A85" s="1">
+        <v>66</v>
+      </c>
+      <c r="B85" s="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A86" s="1">
+        <v>60</v>
+      </c>
+      <c r="B86" s="1">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A87" s="1">
+        <v>58</v>
+      </c>
+      <c r="B87" s="1">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A88" s="1">
+        <v>61</v>
+      </c>
+      <c r="B88" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A89" s="1">
+        <v>67</v>
+      </c>
+      <c r="B89" s="1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A90" s="1">
+        <v>61</v>
+      </c>
+      <c r="B90" s="1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A91" s="1">
+        <v>50</v>
+      </c>
+      <c r="B91" s="1">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A92" s="1">
+        <v>59</v>
+      </c>
+      <c r="B92" s="1">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A93" s="1">
+        <v>56</v>
+      </c>
+      <c r="B93" s="1">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A94" s="1">
+        <v>50</v>
+      </c>
+      <c r="B94" s="1">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A95" s="1">
+        <v>62</v>
+      </c>
+      <c r="B95" s="1">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A96" s="1">
+        <v>56</v>
+      </c>
+      <c r="B96" s="1">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A97" s="1">
+        <v>49</v>
+      </c>
+      <c r="B97" s="1">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A98" s="1">
+        <v>62</v>
+      </c>
+      <c r="B98" s="1">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A99" s="1">
+        <v>44</v>
+      </c>
+      <c r="B99" s="1">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A100" s="1">
+        <v>50</v>
+      </c>
+      <c r="B100" s="1">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
